--- a/Donnees_F.xlsx
+++ b/Donnees_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7F2008-11E1-44A2-A77A-C218B79BA31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2419106C-4639-4572-81EE-E69136EC50EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -762,6 +762,7 @@
         <name val="TIMES"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -779,7 +780,6 @@
         <name val="TIMES"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -812,25 +812,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:Q390" totalsRowShown="0" headerRowDxfId="18" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}" name="Tableau1" displayName="Tableau1" ref="A1:Q390" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A1:Q390" xr:uid="{B22887BA-DDF2-48BF-9437-28C91CB5F792}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{1100C874-2ACC-444F-9559-0BA97B2B95C4}" name="Date" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{60CF5FB0-B425-43F1-A81D-1D127E0F488D}" name="Telephone_Team_Leader" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{B3D7358F-00E0-45C2-8B00-3057DAFF7F96}" name="tata" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{B11ACAA6-0A46-49C7-8EBE-7130FF8F8542}" name="team_leader" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{5490769D-002E-4773-BF92-5A1223D8AA3E}" name="Operation" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{BD3AF168-0C21-4B92-BACC-209D8F48A8A9}" name="zone" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{C4F65627-9090-4A2F-BB27-BF7FD831E373}" name="Prenom_Nom_Promoteur" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{93F83F26-4CD9-4C48-B1D6-248CBC107321}" name="Precisez" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{6A337EF2-4188-4FE0-BDCA-DB89ACA194EE}" name="Produit" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{D8F2A125-354B-4250-9023-1896F65C32B0}" name="Quantites_Cartons" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{9AEA7F94-8C73-415C-BD74-F73E67E5D442}" name="Montant" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{D6C8F247-D787-44A7-8001-A1F630C64806}" name="Transport" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{F9806FE0-2100-48A5-A047-897EB3C10C91}" name="Stationnement" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{93450938-20C3-47CA-ABD7-99C17BE1AB14}" name="Commentaire" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{509AFF8E-3DC8-47BB-8FA2-6E82BE8B87B6}" name="ID_Produit" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{1D80340E-085A-4C8C-AC9C-85DF95DFF70B}" name="Numero_semaine" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{1100C874-2ACC-444F-9559-0BA97B2B95C4}" name="Date" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{60CF5FB0-B425-43F1-A81D-1D127E0F488D}" name="Telephone_Team_Leader" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{B3D7358F-00E0-45C2-8B00-3057DAFF7F96}" name="tata" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{B11ACAA6-0A46-49C7-8EBE-7130FF8F8542}" name="team_leader" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{5490769D-002E-4773-BF92-5A1223D8AA3E}" name="Operation" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{BD3AF168-0C21-4B92-BACC-209D8F48A8A9}" name="zone" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{C4F65627-9090-4A2F-BB27-BF7FD831E373}" name="Prenom_Nom_Promoteur" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{93F83F26-4CD9-4C48-B1D6-248CBC107321}" name="Precisez" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{6A337EF2-4188-4FE0-BDCA-DB89ACA194EE}" name="Produit" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{D8F2A125-354B-4250-9023-1896F65C32B0}" name="Quantites_Cartons" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{9AEA7F94-8C73-415C-BD74-F73E67E5D442}" name="Montant" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{D6C8F247-D787-44A7-8001-A1F630C64806}" name="Transport" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{F9806FE0-2100-48A5-A047-897EB3C10C91}" name="Stationnement" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{93450938-20C3-47CA-ABD7-99C17BE1AB14}" name="Commentaire" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{509AFF8E-3DC8-47BB-8FA2-6E82BE8B87B6}" name="ID_Produit" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{1D80340E-085A-4C8C-AC9C-85DF95DFF70B}" name="Numero_semaine" dataDxfId="1"/>
     <tableColumn id="17" xr3:uid="{68A692AC-E733-4864-875C-0EDC134A1E20}" name="Equipe" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B107" s="1">
         <v>0</v>
